--- a/research/traditional_assets/database/data/canada/canada_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06059999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="E2">
-        <v>0.09039999999999999</v>
+        <v>0.0669</v>
       </c>
       <c r="F2">
-        <v>0.04415</v>
+        <v>0.062</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>1.558516225250823e-05</v>
+        <v>1.494628496733112e-05</v>
       </c>
       <c r="J2">
-        <v>1.213283591304612e-05</v>
+        <v>1.182776281974015e-05</v>
       </c>
       <c r="K2">
-        <v>46277.6</v>
+        <v>48769.3</v>
       </c>
       <c r="L2">
-        <v>0.3194841595846766</v>
+        <v>0.348790123598061</v>
       </c>
       <c r="M2">
-        <v>30909.489</v>
+        <v>39288.467</v>
       </c>
       <c r="N2">
-        <v>0.05873598488915323</v>
+        <v>0.0913563966273316</v>
       </c>
       <c r="O2">
-        <v>0.6679146930696492</v>
+        <v>0.8055983374787008</v>
       </c>
       <c r="P2">
-        <v>18313.489</v>
+        <v>19151.767</v>
       </c>
       <c r="Q2">
-        <v>0.03480034280643313</v>
+        <v>0.04453307944456678</v>
       </c>
       <c r="R2">
-        <v>0.3957311744775011</v>
+        <v>0.3927012895407562</v>
       </c>
       <c r="S2">
-        <v>12596</v>
+        <v>20136.7</v>
       </c>
       <c r="T2">
-        <v>0.4075123985388436</v>
+        <v>0.5125346326187784</v>
       </c>
       <c r="U2">
-        <v>222587.6</v>
+        <v>166268.8</v>
       </c>
       <c r="V2">
-        <v>0.4229737317919712</v>
+        <v>0.3866202883291544</v>
       </c>
       <c r="W2">
-        <v>0.1707824201667232</v>
+        <v>0.156109902492809</v>
       </c>
       <c r="X2">
-        <v>0.07362425762775844</v>
+        <v>0.1240612845524664</v>
       </c>
       <c r="Y2">
-        <v>0.09715816253896474</v>
+        <v>0.0320486179403426</v>
       </c>
       <c r="Z2">
-        <v>0.1318646090428432</v>
+        <v>0.124429640371705</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0368593104432838</v>
+        <v>0.05968410207985742</v>
       </c>
       <c r="AC2">
-        <v>-0.0368593104432838</v>
+        <v>-0.05968410207985742</v>
       </c>
       <c r="AD2">
-        <v>1067265</v>
+        <v>1200391.4</v>
       </c>
       <c r="AE2">
-        <v>8.86236831280965</v>
+        <v>18.9007383073545</v>
       </c>
       <c r="AF2">
-        <v>1067273.862368313</v>
+        <v>1200410.300738307</v>
       </c>
       <c r="AG2">
-        <v>844686.2623683129</v>
+        <v>1034141.500738307</v>
       </c>
       <c r="AH2">
-        <v>0.6697593749607712</v>
+        <v>0.7362369221210668</v>
       </c>
       <c r="AI2">
-        <v>0.7695227582760888</v>
+        <v>0.7880595042557915</v>
       </c>
       <c r="AJ2">
-        <v>0.6161407166245937</v>
+        <v>0.7062849945470866</v>
       </c>
       <c r="AK2">
-        <v>0.7254623552776462</v>
+        <v>0.7620907317875105</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>264830.0248138958</v>
+        <v>204495.9795570699</v>
       </c>
       <c r="AP2">
-        <v>209599.5688258841</v>
+        <v>176174.0205687065</v>
       </c>
     </row>
     <row r="3">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0625</v>
+        <v>0.0418</v>
       </c>
       <c r="E3">
-        <v>0.09039999999999999</v>
+        <v>0.0669</v>
       </c>
       <c r="F3">
-        <v>0.0243</v>
+        <v>0.0616</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -740,85 +740,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>12935.5</v>
+        <v>11581.7</v>
       </c>
       <c r="L3">
-        <v>0.3179231950844854</v>
+        <v>0.3256424026519934</v>
       </c>
       <c r="M3">
-        <v>8796.299999999999</v>
+        <v>13082</v>
       </c>
       <c r="N3">
-        <v>0.058200953176826</v>
+        <v>0.1005768445687197</v>
       </c>
       <c r="O3">
-        <v>0.6800123690618839</v>
+        <v>1.129540568310352</v>
       </c>
       <c r="P3">
-        <v>4970.8</v>
+        <v>4922.6</v>
       </c>
       <c r="Q3">
-        <v>0.03288943056186883</v>
+        <v>0.03784586264133769</v>
       </c>
       <c r="R3">
-        <v>0.3842758300800124</v>
+        <v>0.42503259452412</v>
       </c>
       <c r="S3">
-        <v>3825.499999999999</v>
+        <v>8159.4</v>
       </c>
       <c r="T3">
-        <v>0.4348987642531518</v>
+        <v>0.62371197064669</v>
       </c>
       <c r="U3">
-        <v>90210</v>
+        <v>51622.1</v>
       </c>
       <c r="V3">
-        <v>0.5968768671011078</v>
+        <v>0.3968802880301869</v>
       </c>
       <c r="W3">
-        <v>0.2132427972549039</v>
+        <v>0.156109902492809</v>
       </c>
       <c r="X3">
-        <v>0.07362425762775844</v>
+        <v>0.1162559994386184</v>
       </c>
       <c r="Y3">
-        <v>0.1396185396271454</v>
+        <v>0.03985390305419058</v>
       </c>
       <c r="Z3">
-        <v>0.147439365504316</v>
+        <v>0.1252034758462202</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03630229604482086</v>
+        <v>0.05890741263861228</v>
       </c>
       <c r="AC3">
-        <v>-0.03630229604482086</v>
+        <v>-0.05890741263861228</v>
       </c>
       <c r="AD3">
-        <v>303447.2</v>
+        <v>338945.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>303447.2</v>
+        <v>338945.5</v>
       </c>
       <c r="AG3">
-        <v>213237.2</v>
+        <v>287323.4</v>
       </c>
       <c r="AH3">
-        <v>0.6675273805341544</v>
+        <v>0.7226748727972995</v>
       </c>
       <c r="AI3">
-        <v>0.7920746386819464</v>
+        <v>0.8103507757308017</v>
       </c>
       <c r="AJ3">
-        <v>0.5852153515935142</v>
+        <v>0.6883760177156738</v>
       </c>
       <c r="AK3">
-        <v>0.7280346527740553</v>
+        <v>0.7836491675939866</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.06059999999999999</v>
+        <v>0.0703</v>
       </c>
       <c r="E4">
-        <v>0.101</v>
+        <v>0.109</v>
       </c>
       <c r="F4">
-        <v>0.063</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -865,85 +865,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>11532.1</v>
+        <v>12780.7</v>
       </c>
       <c r="L4">
-        <v>0.333153257258414</v>
+        <v>0.3650752390854766</v>
       </c>
       <c r="M4">
-        <v>13404.5</v>
+        <v>14300.374</v>
       </c>
       <c r="N4">
-        <v>0.0959999369764299</v>
+        <v>0.1217391903959655</v>
       </c>
       <c r="O4">
-        <v>1.162364183453144</v>
+        <v>1.118903815909927</v>
       </c>
       <c r="P4">
-        <v>4646.099999999999</v>
+        <v>4732.974</v>
       </c>
       <c r="Q4">
-        <v>0.03327429648149435</v>
+        <v>0.04029184292139174</v>
       </c>
       <c r="R4">
-        <v>0.4028841234467269</v>
+        <v>0.3703219698451571</v>
       </c>
       <c r="S4">
-        <v>8758.400000000001</v>
+        <v>9567.4</v>
       </c>
       <c r="T4">
-        <v>0.6533925174381738</v>
+        <v>0.6690314533032492</v>
       </c>
       <c r="U4">
-        <v>4603.8</v>
+        <v>6274.1</v>
       </c>
       <c r="V4">
-        <v>0.03297135363885919</v>
+        <v>0.05341146004036868</v>
       </c>
       <c r="W4">
-        <v>0.1707824201667232</v>
+        <v>0.1652728728102221</v>
       </c>
       <c r="X4">
-        <v>0.07039313757763853</v>
+        <v>0.1125009757040382</v>
       </c>
       <c r="Y4">
-        <v>0.1003892825890847</v>
+        <v>0.05277189710618382</v>
       </c>
       <c r="Z4">
-        <v>0.106981802739958</v>
+        <v>0.1103698488957939</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03638229114938447</v>
+        <v>0.05903852803230139</v>
       </c>
       <c r="AC4">
-        <v>-0.03638229114938447</v>
+        <v>-0.05903852803230139</v>
       </c>
       <c r="AD4">
-        <v>254378.8</v>
+        <v>283672.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>254378.8</v>
+        <v>283672.4</v>
       </c>
       <c r="AG4">
-        <v>249775</v>
+        <v>277398.3</v>
       </c>
       <c r="AH4">
-        <v>0.6456165606327366</v>
+        <v>0.7071661069697166</v>
       </c>
       <c r="AI4">
-        <v>0.7595945624740958</v>
+        <v>0.7764411885058007</v>
       </c>
       <c r="AJ4">
-        <v>0.6414268116022047</v>
+        <v>0.7025132095578851</v>
       </c>
       <c r="AK4">
-        <v>0.7562435699238049</v>
+        <v>0.7725349606238691</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0727</v>
+        <v>0.061</v>
       </c>
       <c r="E5">
-        <v>0.08500000000000001</v>
+        <v>0.05769999999999999</v>
       </c>
       <c r="F5">
-        <v>0.0268</v>
+        <v>-0.0224</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -990,85 +990,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>5185.3</v>
+        <v>4561.1</v>
       </c>
       <c r="L5">
-        <v>0.3237615354837098</v>
+        <v>0.2993829996718084</v>
       </c>
       <c r="M5">
-        <v>2136.31</v>
+        <v>2272.94</v>
       </c>
       <c r="N5">
-        <v>0.04065738939787836</v>
+        <v>0.061983806882484</v>
       </c>
       <c r="O5">
-        <v>0.4119935201434825</v>
+        <v>0.4983315428295805</v>
       </c>
       <c r="P5">
-        <v>2124.21</v>
+        <v>2174.64</v>
       </c>
       <c r="Q5">
-        <v>0.04042710708317949</v>
+        <v>0.05930313417816792</v>
       </c>
       <c r="R5">
-        <v>0.4096600003857057</v>
+        <v>0.4767797241893402</v>
       </c>
       <c r="S5">
-        <v>12.09999999999991</v>
+        <v>98.30000000000018</v>
       </c>
       <c r="T5">
-        <v>0.005663971989083939</v>
+        <v>0.04324795199169366</v>
       </c>
       <c r="U5">
-        <v>27525.3</v>
+        <v>22763.1</v>
       </c>
       <c r="V5">
-        <v>0.52385039642815</v>
+        <v>0.6207570786939697</v>
       </c>
       <c r="W5">
-        <v>0.1800170112308841</v>
+        <v>0.1320561334835013</v>
       </c>
       <c r="X5">
-        <v>0.08669293051325146</v>
+        <v>0.1451838646850144</v>
       </c>
       <c r="Y5">
-        <v>0.09332408071763261</v>
+        <v>-0.01312773120151309</v>
       </c>
       <c r="Z5">
-        <v>0.1325240790388243</v>
+        <v>0.1013449239730137</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03676496798124326</v>
+        <v>0.05937234335422405</v>
       </c>
       <c r="AC5">
-        <v>-0.03676496798124326</v>
+        <v>-0.05937234335422405</v>
       </c>
       <c r="AD5">
-        <v>145017.9</v>
+        <v>149505.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>145017.9</v>
+        <v>149505.8</v>
       </c>
       <c r="AG5">
-        <v>117492.6</v>
+        <v>126742.7</v>
       </c>
       <c r="AH5">
-        <v>0.7340370445545983</v>
+        <v>0.8030360568001087</v>
       </c>
       <c r="AI5">
-        <v>0.7968791470379263</v>
+        <v>0.8018507821630252</v>
       </c>
       <c r="AJ5">
-        <v>0.690983363601291</v>
+        <v>0.7755993111914259</v>
       </c>
       <c r="AK5">
-        <v>0.7606816136529907</v>
+        <v>0.7742953353884651</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.059</v>
+        <v>0.0934</v>
       </c>
       <c r="E6">
-        <v>0.109</v>
+        <v>0.205</v>
       </c>
       <c r="F6">
-        <v>0.06150000000000001</v>
+        <v>0.0624</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1115,85 +1115,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>6254</v>
+        <v>9926.700000000001</v>
       </c>
       <c r="L6">
-        <v>0.2865573710400191</v>
+        <v>0.4056035204850882</v>
       </c>
       <c r="M6">
-        <v>2216.844</v>
+        <v>2817.869</v>
       </c>
       <c r="N6">
-        <v>0.03177783479810266</v>
+        <v>0.04422392660181864</v>
       </c>
       <c r="O6">
-        <v>0.3544681803645667</v>
+        <v>0.2838676498735733</v>
       </c>
       <c r="P6">
-        <v>2216.844</v>
+        <v>2805.369</v>
       </c>
       <c r="Q6">
-        <v>0.03177783479810266</v>
+        <v>0.04402775031309736</v>
       </c>
       <c r="R6">
-        <v>0.3544681803645667</v>
+        <v>0.2826084197165221</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.004435976264333083</v>
       </c>
       <c r="U6">
-        <v>75131.5</v>
+        <v>64074.9</v>
       </c>
       <c r="V6">
-        <v>1.076988906361318</v>
+        <v>1.00559808657495</v>
       </c>
       <c r="W6">
-        <v>0.1603363628206279</v>
+        <v>0.2284541881081479</v>
       </c>
       <c r="X6">
-        <v>0.07908150015543239</v>
+        <v>0.1268361399318653</v>
       </c>
       <c r="Y6">
-        <v>0.08125486266519547</v>
+        <v>0.1016180481762827</v>
       </c>
       <c r="Z6">
-        <v>0.1590727039356729</v>
+        <v>0.189866749831653</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.0368593104432838</v>
+        <v>0.05968410207985742</v>
       </c>
       <c r="AC6">
-        <v>-0.0368593104432838</v>
+        <v>-0.05968410207985742</v>
       </c>
       <c r="AD6">
-        <v>161974.1</v>
+        <v>200327.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>161974.1</v>
+        <v>200327.1</v>
       </c>
       <c r="AG6">
-        <v>86842.60000000001</v>
+        <v>136252.2</v>
       </c>
       <c r="AH6">
-        <v>0.6989632113950948</v>
+        <v>0.7586845893488732</v>
       </c>
       <c r="AI6">
-        <v>0.7773403605900285</v>
+        <v>0.7936286146220256</v>
       </c>
       <c r="AJ6">
-        <v>0.5545387613160132</v>
+        <v>0.6813618415525498</v>
       </c>
       <c r="AK6">
-        <v>0.651785037463008</v>
+        <v>0.7234208839874634</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.04219999999999999</v>
+        <v>0.0365</v>
       </c>
       <c r="E7">
-        <v>0.0622</v>
+        <v>0.0438</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1237,85 +1237,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>7762.3</v>
+        <v>7271.4</v>
       </c>
       <c r="L7">
-        <v>0.3269575839265406</v>
+        <v>0.3327415000228801</v>
       </c>
       <c r="M7">
-        <v>3525.5</v>
+        <v>5669.200000000001</v>
       </c>
       <c r="N7">
-        <v>0.04097655659774283</v>
+        <v>0.09707850084163698</v>
       </c>
       <c r="O7">
-        <v>0.4541823943934143</v>
+        <v>0.7796572874549607</v>
       </c>
       <c r="P7">
-        <v>3525.5</v>
+        <v>3562.4</v>
       </c>
       <c r="Q7">
-        <v>0.04097655659774283</v>
+        <v>0.06100198465361031</v>
       </c>
       <c r="R7">
-        <v>0.4541823943934143</v>
+        <v>0.4899194102923784</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2106.800000000001</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.3716220983560291</v>
       </c>
       <c r="U7">
-        <v>3205.3</v>
+        <v>3745</v>
       </c>
       <c r="V7">
-        <v>0.03725490196078431</v>
+        <v>0.06412879871091696</v>
       </c>
       <c r="W7">
-        <v>0.156338808269806</v>
+        <v>0.128787382329239</v>
       </c>
       <c r="X7">
-        <v>0.07097567467963271</v>
+        <v>0.1240612845524664</v>
       </c>
       <c r="Y7">
-        <v>0.08536313359017324</v>
+        <v>0.004726097776772673</v>
       </c>
       <c r="Z7">
-        <v>0.1193764327459798</v>
+        <v>0.1058815549127627</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.03699161072409801</v>
+        <v>0.05974390503300162</v>
       </c>
       <c r="AC7">
-        <v>-0.03699161072409801</v>
+        <v>-0.05974390503300162</v>
       </c>
       <c r="AD7">
-        <v>159627</v>
+        <v>175359.7</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>159627</v>
+        <v>175359.7</v>
       </c>
       <c r="AG7">
-        <v>156421.7</v>
+        <v>171614.7</v>
       </c>
       <c r="AH7">
-        <v>0.6497777452129738</v>
+        <v>0.7501768924929991</v>
       </c>
       <c r="AI7">
-        <v>0.7308309506749657</v>
+        <v>0.7618600957279543</v>
       </c>
       <c r="AJ7">
-        <v>0.6451478128027578</v>
+        <v>0.7461093469580823</v>
       </c>
       <c r="AK7">
-        <v>0.7268220536658532</v>
+        <v>0.7579213887322289</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.108</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="E8">
-        <v>0.219</v>
+        <v>0.118</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1353,91 +1353,91 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.0003136106601983844</v>
+        <v>0.000299770829596084</v>
       </c>
       <c r="J8">
-        <v>0.0002446780000890114</v>
+        <v>0.0002371078968781704</v>
       </c>
       <c r="K8">
-        <v>2562.4</v>
+        <v>2481.5</v>
       </c>
       <c r="L8">
-        <v>0.3559630478571925</v>
+        <v>0.3559492218317435</v>
       </c>
       <c r="M8">
-        <v>773.7909999999999</v>
+        <v>1065.484</v>
       </c>
       <c r="N8">
-        <v>0.03004780211245728</v>
+        <v>0.04693824147455693</v>
       </c>
       <c r="O8">
-        <v>0.3019790040586949</v>
+        <v>0.4293709449929478</v>
       </c>
       <c r="P8">
-        <v>773.7909999999999</v>
+        <v>885.784</v>
       </c>
       <c r="Q8">
-        <v>0.03004780211245728</v>
+        <v>0.03902183729300387</v>
       </c>
       <c r="R8">
-        <v>0.3019790040586949</v>
+        <v>0.3569550674994963</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>179.6999999999999</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.1686557470595522</v>
       </c>
       <c r="U8">
-        <v>21856</v>
+        <v>17731.2</v>
       </c>
       <c r="V8">
-        <v>0.8487107797452625</v>
+        <v>0.7811204553364142</v>
       </c>
       <c r="W8">
-        <v>0.2447724124755218</v>
+        <v>0.1806724524565338</v>
       </c>
       <c r="X8">
-        <v>0.05966387812344474</v>
+        <v>0.1001673471151005</v>
       </c>
       <c r="Y8">
-        <v>0.1851085343520771</v>
+        <v>0.08050510534143324</v>
       </c>
       <c r="Z8">
-        <v>0.2378170791155974</v>
+        <v>0.3028532358098486</v>
       </c>
       <c r="AA8">
-        <v>5.818860730501457e-05</v>
+        <v>7.180889380562179e-05</v>
       </c>
       <c r="AB8">
-        <v>0.03770031194890259</v>
+        <v>0.06142322449710087</v>
       </c>
       <c r="AC8">
-        <v>-0.03764212334159758</v>
+        <v>-0.06135141560329525</v>
       </c>
       <c r="AD8">
-        <v>31004</v>
+        <v>40560.2</v>
       </c>
       <c r="AE8">
-        <v>8.86236831280965</v>
+        <v>18.9007383073545</v>
       </c>
       <c r="AF8">
-        <v>31012.86236831281</v>
+        <v>40579.10073830735</v>
       </c>
       <c r="AG8">
-        <v>9156.86236831281</v>
+        <v>22847.90073830735</v>
       </c>
       <c r="AH8">
-        <v>0.5463390744628099</v>
+        <v>0.6412748071210176</v>
       </c>
       <c r="AI8">
-        <v>0.6709652826265907</v>
+        <v>0.7178914294862634</v>
       </c>
       <c r="AJ8">
-        <v>0.2623076705193522</v>
+        <v>0.501626877551233</v>
       </c>
       <c r="AK8">
-        <v>0.3758162842613741</v>
+        <v>0.588951449017641</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1446,10 +1446,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>7693.300248138958</v>
+        <v>6909.744463373083</v>
       </c>
       <c r="AP8">
-        <v>2272.174284941144</v>
+        <v>3892.316991193757</v>
       </c>
     </row>
     <row r="9">
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0163</v>
+        <v>0.00371</v>
       </c>
       <c r="E9">
-        <v>-0.178</v>
+        <v>0.0188</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1487,85 +1487,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>46</v>
+        <v>166.2</v>
       </c>
       <c r="L9">
-        <v>0.05984907624251887</v>
+        <v>0.231896190874843</v>
       </c>
       <c r="M9">
-        <v>56.24400000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="N9">
-        <v>0.04065047701647876</v>
+        <v>0.07793463546702764</v>
       </c>
       <c r="O9">
-        <v>1.222695652173913</v>
+        <v>0.4849578820697954</v>
       </c>
       <c r="P9">
-        <v>56.24400000000001</v>
+        <v>68</v>
       </c>
       <c r="Q9">
-        <v>0.04065047701647876</v>
+        <v>0.06575130535679752</v>
       </c>
       <c r="R9">
-        <v>1.222695652173913</v>
+        <v>0.4091456077015644</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>12.59999999999999</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.1563275434243176</v>
       </c>
       <c r="U9">
-        <v>55.7</v>
+        <v>58.4</v>
       </c>
       <c r="V9">
-        <v>0.04025729979762938</v>
+        <v>0.05646876812995551</v>
       </c>
       <c r="W9">
-        <v>0.02585722315907813</v>
+        <v>0.08180744240992321</v>
       </c>
       <c r="X9">
-        <v>0.1871222453785448</v>
+        <v>0.2935618483325673</v>
       </c>
       <c r="Y9">
-        <v>-0.1612650222194666</v>
+        <v>-0.2117544059226441</v>
       </c>
       <c r="Z9">
-        <v>0.06531770784645324</v>
+        <v>0.05183299462649435</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04001806579372379</v>
+        <v>0.06386219224548187</v>
       </c>
       <c r="AC9">
-        <v>-0.04001806579372379</v>
+        <v>-0.06386219224548187</v>
       </c>
       <c r="AD9">
-        <v>11816</v>
+        <v>12020.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>11816</v>
+        <v>12020.7</v>
       </c>
       <c r="AG9">
-        <v>11760.3</v>
+        <v>11962.3</v>
       </c>
       <c r="AH9">
-        <v>0.8951786417770236</v>
+        <v>0.9207807030310458</v>
       </c>
       <c r="AI9">
-        <v>0.8472680338448301</v>
+        <v>0.8549512450124822</v>
       </c>
       <c r="AJ9">
-        <v>0.8947344395499053</v>
+        <v>0.9204247297349286</v>
       </c>
       <c r="AK9">
-        <v>0.846655579793093</v>
+        <v>0.8543462579543913</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/research/traditional_assets/database/data/canada/canada_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.061</v>
+        <v>0.0539</v>
       </c>
       <c r="E2">
-        <v>0.0669</v>
+        <v>-0.0106</v>
       </c>
       <c r="F2">
-        <v>0.062</v>
+        <v>0.0442</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>1.494628496733112e-05</v>
+        <v>1.699213933192129e-05</v>
       </c>
       <c r="J2">
-        <v>1.182776281974015e-05</v>
+        <v>1.3398023285596e-05</v>
       </c>
       <c r="K2">
-        <v>48769.3</v>
+        <v>33069.1</v>
       </c>
       <c r="L2">
-        <v>0.348790123598061</v>
+        <v>0.2377462451678396</v>
       </c>
       <c r="M2">
-        <v>39288.467</v>
+        <v>30490.04</v>
       </c>
       <c r="N2">
-        <v>0.0913563966273316</v>
+        <v>0.06601070285610118</v>
       </c>
       <c r="O2">
-        <v>0.8055983374787008</v>
+        <v>0.9220099730564182</v>
       </c>
       <c r="P2">
-        <v>19151.767</v>
+        <v>18740.34</v>
       </c>
       <c r="Q2">
-        <v>0.04453307944456678</v>
+        <v>0.0405726924320961</v>
       </c>
       <c r="R2">
-        <v>0.3927012895407562</v>
+        <v>0.5667024503237161</v>
       </c>
       <c r="S2">
-        <v>20136.7</v>
+        <v>11749.7</v>
       </c>
       <c r="T2">
-        <v>0.5125346326187784</v>
+        <v>0.3853619083477753</v>
       </c>
       <c r="U2">
-        <v>166268.8</v>
+        <v>140597.1</v>
       </c>
       <c r="V2">
-        <v>0.3866202883291544</v>
+        <v>0.3043916436491899</v>
       </c>
       <c r="W2">
-        <v>0.156109902492809</v>
+        <v>0.100071285209157</v>
       </c>
       <c r="X2">
-        <v>0.1240612845524664</v>
+        <v>0.09370581980287165</v>
       </c>
       <c r="Y2">
-        <v>0.0320486179403426</v>
+        <v>0.006365465406285339</v>
       </c>
       <c r="Z2">
-        <v>0.124429640371705</v>
+        <v>0.1055184962194647</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05968410207985742</v>
+        <v>0.05061526714808874</v>
       </c>
       <c r="AC2">
-        <v>-0.05968410207985742</v>
+        <v>-0.05061526714808874</v>
       </c>
       <c r="AD2">
-        <v>1200391.4</v>
+        <v>1278458.2</v>
       </c>
       <c r="AE2">
-        <v>18.9007383073545</v>
+        <v>13.38246836275903</v>
       </c>
       <c r="AF2">
-        <v>1200410.300738307</v>
+        <v>1278471.582468363</v>
       </c>
       <c r="AG2">
-        <v>1034141.500738307</v>
+        <v>1137874.482468363</v>
       </c>
       <c r="AH2">
-        <v>0.7362369221210668</v>
+        <v>0.7345988491778361</v>
       </c>
       <c r="AI2">
-        <v>0.7880595042557915</v>
+        <v>0.7923568596509138</v>
       </c>
       <c r="AJ2">
-        <v>0.7062849945470866</v>
+        <v>0.7112738494068164</v>
       </c>
       <c r="AK2">
-        <v>0.7620907317875105</v>
+        <v>0.7725361854053631</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>204495.9795570699</v>
+        <v>253662.3412698413</v>
       </c>
       <c r="AP2">
-        <v>176174.0205687065</v>
+        <v>225768.7465215005</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada (TSX:RY)</t>
+          <t>The Toronto-Dominion Bank (TSX:TD)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0418</v>
+        <v>0.0621</v>
       </c>
       <c r="E3">
-        <v>0.0669</v>
+        <v>-0.008670000000000001</v>
       </c>
       <c r="F3">
-        <v>0.0616</v>
+        <v>0.018</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -740,85 +740,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>11581.7</v>
+        <v>7763.1</v>
       </c>
       <c r="L3">
-        <v>0.3256424026519934</v>
+        <v>0.2191424675863587</v>
       </c>
       <c r="M3">
-        <v>13082</v>
+        <v>13758.032</v>
       </c>
       <c r="N3">
-        <v>0.1005768445687197</v>
+        <v>0.1185058546476272</v>
       </c>
       <c r="O3">
-        <v>1.129540568310352</v>
+        <v>1.772234287848926</v>
       </c>
       <c r="P3">
-        <v>4922.6</v>
+        <v>4942.331999999999</v>
       </c>
       <c r="Q3">
-        <v>0.03784586264133769</v>
+        <v>0.04257115244479128</v>
       </c>
       <c r="R3">
-        <v>0.42503259452412</v>
+        <v>0.6366441241256714</v>
       </c>
       <c r="S3">
-        <v>8159.4</v>
+        <v>8815.700000000001</v>
       </c>
       <c r="T3">
-        <v>0.62371197064669</v>
+        <v>0.6407675167494887</v>
       </c>
       <c r="U3">
-        <v>51622.1</v>
+        <v>4839.2</v>
       </c>
       <c r="V3">
-        <v>0.3968802880301869</v>
+        <v>0.04168281712172189</v>
       </c>
       <c r="W3">
-        <v>0.156109902492809</v>
+        <v>0.100071285209157</v>
       </c>
       <c r="X3">
-        <v>0.1162559994386184</v>
+        <v>0.09327393304184414</v>
       </c>
       <c r="Y3">
-        <v>0.03985390305419058</v>
+        <v>0.006797352167312851</v>
       </c>
       <c r="Z3">
-        <v>0.1252034758462202</v>
+        <v>0.1023461827149593</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05890741263861228</v>
+        <v>0.05002928962713915</v>
       </c>
       <c r="AC3">
-        <v>-0.05890741263861228</v>
+        <v>-0.05002928962713915</v>
       </c>
       <c r="AD3">
-        <v>338945.5</v>
+        <v>317231.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>338945.5</v>
+        <v>317231.2</v>
       </c>
       <c r="AG3">
-        <v>287323.4</v>
+        <v>312392</v>
       </c>
       <c r="AH3">
-        <v>0.7226748727972995</v>
+        <v>0.732082699670226</v>
       </c>
       <c r="AI3">
-        <v>0.8103507757308017</v>
+        <v>0.7971658665637388</v>
       </c>
       <c r="AJ3">
-        <v>0.6883760177156738</v>
+        <v>0.7290569299756026</v>
       </c>
       <c r="AK3">
-        <v>0.7836491675939866</v>
+        <v>0.7946689676365065</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank (TSX:TD)</t>
+          <t>Royal Bank of Canada (TSX:RY)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0703</v>
+        <v>0.0539</v>
       </c>
       <c r="E4">
-        <v>0.109</v>
+        <v>0.0368</v>
       </c>
       <c r="F4">
-        <v>0.08740000000000001</v>
+        <v>0.0516</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -865,85 +865,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>12780.7</v>
+        <v>10698.5</v>
       </c>
       <c r="L4">
-        <v>0.3650752390854766</v>
+        <v>0.2769035257090501</v>
       </c>
       <c r="M4">
-        <v>14300.374</v>
+        <v>6759.4</v>
       </c>
       <c r="N4">
-        <v>0.1217391903959655</v>
+        <v>0.04736309204740934</v>
       </c>
       <c r="O4">
-        <v>1.118903815909927</v>
+        <v>0.6318081974108519</v>
       </c>
       <c r="P4">
-        <v>4732.974</v>
+        <v>3825.4</v>
       </c>
       <c r="Q4">
-        <v>0.04029184292139174</v>
+        <v>0.02680456435751098</v>
       </c>
       <c r="R4">
-        <v>0.3703219698451571</v>
+        <v>0.3575641445062392</v>
       </c>
       <c r="S4">
-        <v>9567.4</v>
+        <v>2934</v>
       </c>
       <c r="T4">
-        <v>0.6690314533032492</v>
+        <v>0.434062194869367</v>
       </c>
       <c r="U4">
-        <v>6274.1</v>
+        <v>43192.4</v>
       </c>
       <c r="V4">
-        <v>0.05341146004036868</v>
+        <v>0.302648995021529</v>
       </c>
       <c r="W4">
-        <v>0.1652728728102221</v>
+        <v>0.1448150303883482</v>
       </c>
       <c r="X4">
-        <v>0.1125009757040382</v>
+        <v>0.09116715327413334</v>
       </c>
       <c r="Y4">
-        <v>0.05277189710618382</v>
+        <v>0.05364787711421486</v>
       </c>
       <c r="Z4">
-        <v>0.1103698488957939</v>
+        <v>0.1080539427906612</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05903852803230139</v>
+        <v>0.05014077194846574</v>
       </c>
       <c r="AC4">
-        <v>-0.05903852803230139</v>
+        <v>-0.05014077194846574</v>
       </c>
       <c r="AD4">
-        <v>283672.4</v>
+        <v>367375.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>283672.4</v>
+        <v>367375.2</v>
       </c>
       <c r="AG4">
-        <v>277398.3</v>
+        <v>324182.8</v>
       </c>
       <c r="AH4">
-        <v>0.7071661069697166</v>
+        <v>0.7202168559765076</v>
       </c>
       <c r="AI4">
-        <v>0.7764411885058007</v>
+        <v>0.812484173292413</v>
       </c>
       <c r="AJ4">
-        <v>0.7025132095578851</v>
+        <v>0.6943342786518577</v>
       </c>
       <c r="AK4">
-        <v>0.7725349606238691</v>
+        <v>0.7926801566372146</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.061</v>
+        <v>0.0467</v>
       </c>
       <c r="E5">
-        <v>0.05769999999999999</v>
+        <v>-0.0106</v>
       </c>
       <c r="F5">
-        <v>-0.0224</v>
+        <v>0.0368</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -990,85 +990,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>4561.1</v>
+        <v>3596.4</v>
       </c>
       <c r="L5">
-        <v>0.2993829996718084</v>
+        <v>0.234361865041869</v>
       </c>
       <c r="M5">
-        <v>2272.94</v>
+        <v>2309.128</v>
       </c>
       <c r="N5">
-        <v>0.061983806882484</v>
+        <v>0.05133654363475485</v>
       </c>
       <c r="O5">
-        <v>0.4983315428295805</v>
+        <v>0.6420665109553999</v>
       </c>
       <c r="P5">
-        <v>2174.64</v>
+        <v>2309.128</v>
       </c>
       <c r="Q5">
-        <v>0.05930313417816792</v>
+        <v>0.05133654363475485</v>
       </c>
       <c r="R5">
-        <v>0.4767797241893402</v>
+        <v>0.6420665109553999</v>
       </c>
       <c r="S5">
-        <v>98.30000000000018</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.04324795199169366</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>22763.1</v>
+        <v>14634.1</v>
       </c>
       <c r="V5">
-        <v>0.6207570786939697</v>
+        <v>0.3253453741868645</v>
       </c>
       <c r="W5">
-        <v>0.1320561334835013</v>
+        <v>0.1031249462353258</v>
       </c>
       <c r="X5">
-        <v>0.1451838646850144</v>
+        <v>0.1023142611331278</v>
       </c>
       <c r="Y5">
-        <v>-0.01312773120151309</v>
+        <v>0.0008106851021980749</v>
       </c>
       <c r="Z5">
-        <v>0.1013449239730137</v>
+        <v>0.096138545257257</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05937234335422405</v>
+        <v>0.05049035222616338</v>
       </c>
       <c r="AC5">
-        <v>-0.05937234335422405</v>
+        <v>-0.05049035222616338</v>
       </c>
       <c r="AD5">
-        <v>149505.8</v>
+        <v>153461.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>149505.8</v>
+        <v>153461.8</v>
       </c>
       <c r="AG5">
-        <v>126742.7</v>
+        <v>138827.7</v>
       </c>
       <c r="AH5">
-        <v>0.8030360568001087</v>
+        <v>0.7733332661432559</v>
       </c>
       <c r="AI5">
-        <v>0.8018507821630252</v>
+        <v>0.8002162946863883</v>
       </c>
       <c r="AJ5">
-        <v>0.7755993111914259</v>
+        <v>0.7552869055138545</v>
       </c>
       <c r="AK5">
-        <v>0.7742953353884651</v>
+        <v>0.7837116471427047</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bank of Montreal (TSX:BMO)</t>
+          <t>The Bank of Nova Scotia (TSX:BNS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1094,13 +1094,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0934</v>
+        <v>0.0226</v>
       </c>
       <c r="E6">
-        <v>0.205</v>
-      </c>
-      <c r="F6">
-        <v>0.0624</v>
+        <v>-0.0282</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1115,85 +1112,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>9926.700000000001</v>
+        <v>5335.2</v>
       </c>
       <c r="L6">
-        <v>0.4056035204850882</v>
+        <v>0.2533140881984275</v>
       </c>
       <c r="M6">
-        <v>2817.869</v>
+        <v>3602.2</v>
       </c>
       <c r="N6">
-        <v>0.04422392660181864</v>
+        <v>0.06075120205483495</v>
       </c>
       <c r="O6">
-        <v>0.2838676498735733</v>
+        <v>0.6751761883340831</v>
       </c>
       <c r="P6">
-        <v>2805.369</v>
+        <v>3602.2</v>
       </c>
       <c r="Q6">
-        <v>0.04402775031309736</v>
+        <v>0.06075120205483495</v>
       </c>
       <c r="R6">
-        <v>0.2826084197165221</v>
+        <v>0.6751761883340831</v>
       </c>
       <c r="S6">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.004435976264333083</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>64074.9</v>
+        <v>3178.8</v>
       </c>
       <c r="V6">
-        <v>1.00559808657495</v>
+        <v>0.05361054941200082</v>
       </c>
       <c r="W6">
-        <v>0.2284541881081479</v>
+        <v>0.09976849341197326</v>
       </c>
       <c r="X6">
-        <v>0.1268361399318653</v>
+        <v>0.09865756493975505</v>
       </c>
       <c r="Y6">
-        <v>0.1016180481762827</v>
+        <v>0.001110928472218206</v>
       </c>
       <c r="Z6">
-        <v>0.189866749831653</v>
+        <v>0.09625819000819</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05968410207985742</v>
+        <v>0.05061526714808874</v>
       </c>
       <c r="AC6">
-        <v>-0.05968410207985742</v>
+        <v>-0.05061526714808874</v>
       </c>
       <c r="AD6">
-        <v>200327.1</v>
+        <v>186006.7</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>200327.1</v>
+        <v>186006.7</v>
       </c>
       <c r="AG6">
-        <v>136252.2</v>
+        <v>182827.9</v>
       </c>
       <c r="AH6">
-        <v>0.7586845893488732</v>
+        <v>0.7582794199779047</v>
       </c>
       <c r="AI6">
-        <v>0.7936286146220256</v>
+        <v>0.7665723047402547</v>
       </c>
       <c r="AJ6">
-        <v>0.6813618415525498</v>
+        <v>0.7551058928094987</v>
       </c>
       <c r="AK6">
-        <v>0.7234208839874634</v>
+        <v>0.7634736927821405</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1210,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia (TSX:BNS)</t>
+          <t>Bank of Montreal (TSX:BMO)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1219,10 +1216,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0365</v>
+        <v>0.0546</v>
       </c>
       <c r="E7">
-        <v>0.0438</v>
+        <v>-0.0435</v>
+      </c>
+      <c r="F7">
+        <v>0.0635</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1237,85 +1237,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>7271.4</v>
+        <v>3142.8</v>
       </c>
       <c r="L7">
-        <v>0.3327415000228801</v>
+        <v>0.150407029331955</v>
       </c>
       <c r="M7">
-        <v>5669.200000000001</v>
+        <v>3030.5</v>
       </c>
       <c r="N7">
-        <v>0.09707850084163698</v>
+        <v>0.04210244070509259</v>
       </c>
       <c r="O7">
-        <v>0.7796572874549607</v>
+        <v>0.9642675321369479</v>
       </c>
       <c r="P7">
-        <v>3562.4</v>
+        <v>3030.5</v>
       </c>
       <c r="Q7">
-        <v>0.06100198465361031</v>
+        <v>0.04210244070509259</v>
       </c>
       <c r="R7">
-        <v>0.4899194102923784</v>
+        <v>0.9642675321369479</v>
       </c>
       <c r="S7">
-        <v>2106.800000000001</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.3716220983560291</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>3745</v>
+        <v>56022.8</v>
       </c>
       <c r="V7">
-        <v>0.06412879871091696</v>
+        <v>0.7783192922399805</v>
       </c>
       <c r="W7">
-        <v>0.128787382329239</v>
+        <v>0.06266937061431059</v>
       </c>
       <c r="X7">
-        <v>0.1240612845524664</v>
+        <v>0.09370581980287165</v>
       </c>
       <c r="Y7">
-        <v>0.004726097776772673</v>
+        <v>-0.03103644918856106</v>
       </c>
       <c r="Z7">
-        <v>0.1058815549127627</v>
+        <v>0.1132728136140095</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05974390503300162</v>
+        <v>0.05081348245462826</v>
       </c>
       <c r="AC7">
-        <v>-0.05974390503300162</v>
+        <v>-0.05081348245462826</v>
       </c>
       <c r="AD7">
-        <v>175359.7</v>
+        <v>199018.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>175359.7</v>
+        <v>199018.6</v>
       </c>
       <c r="AG7">
-        <v>171614.7</v>
+        <v>142995.8</v>
       </c>
       <c r="AH7">
-        <v>0.7501768924929991</v>
+        <v>0.7343919397131637</v>
       </c>
       <c r="AI7">
-        <v>0.7618600957279543</v>
+        <v>0.7820426774638722</v>
       </c>
       <c r="AJ7">
-        <v>0.7461093469580823</v>
+        <v>0.6651740900104662</v>
       </c>
       <c r="AK7">
-        <v>0.7579213887322289</v>
+        <v>0.7205168928383556</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.08359999999999999</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="E8">
-        <v>0.118</v>
+        <v>0.0924</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1353,91 +1353,91 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.000299770829596084</v>
+        <v>0.0003358875490219984</v>
       </c>
       <c r="J8">
-        <v>0.0002371078968781704</v>
+        <v>0.0002820262147160826</v>
       </c>
       <c r="K8">
-        <v>2481.5</v>
+        <v>2402.7</v>
       </c>
       <c r="L8">
-        <v>0.3559492218317435</v>
+        <v>0.3414575220987408</v>
       </c>
       <c r="M8">
-        <v>1065.484</v>
+        <v>972.3560000000001</v>
       </c>
       <c r="N8">
-        <v>0.04693824147455693</v>
+        <v>0.03752777852823009</v>
       </c>
       <c r="O8">
-        <v>0.4293709449929478</v>
+        <v>0.4046930536479794</v>
       </c>
       <c r="P8">
-        <v>885.784</v>
+        <v>972.3560000000001</v>
       </c>
       <c r="Q8">
-        <v>0.03902183729300387</v>
+        <v>0.03752777852823009</v>
       </c>
       <c r="R8">
-        <v>0.3569550674994963</v>
+        <v>0.4046930536479794</v>
       </c>
       <c r="S8">
-        <v>179.6999999999999</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0.1686557470595522</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>17731.2</v>
+        <v>18679.8</v>
       </c>
       <c r="V8">
-        <v>0.7811204553364142</v>
+        <v>0.7209410929244354</v>
       </c>
       <c r="W8">
-        <v>0.1806724524565338</v>
+        <v>0.1630618463647531</v>
       </c>
       <c r="X8">
-        <v>0.1001673471151005</v>
+        <v>0.07900217716469986</v>
       </c>
       <c r="Y8">
-        <v>0.08050510534143324</v>
+        <v>0.08405966920005321</v>
       </c>
       <c r="Z8">
-        <v>0.3028532358098486</v>
+        <v>0.1867795832738809</v>
       </c>
       <c r="AA8">
-        <v>7.180889380562179e-05</v>
+        <v>5.267673885697998e-05</v>
       </c>
       <c r="AB8">
-        <v>0.06142322449710087</v>
+        <v>0.05241320603286936</v>
       </c>
       <c r="AC8">
-        <v>-0.06135141560329525</v>
+        <v>-0.05236052929401239</v>
       </c>
       <c r="AD8">
-        <v>40560.2</v>
+        <v>43001.6</v>
       </c>
       <c r="AE8">
-        <v>18.9007383073545</v>
+        <v>13.38246836275903</v>
       </c>
       <c r="AF8">
-        <v>40579.10073830735</v>
+        <v>43014.98246836276</v>
       </c>
       <c r="AG8">
-        <v>22847.90073830735</v>
+        <v>24335.18246836276</v>
       </c>
       <c r="AH8">
-        <v>0.6412748071210176</v>
+        <v>0.6240813374701362</v>
       </c>
       <c r="AI8">
-        <v>0.7178914294862634</v>
+        <v>0.7161610338399358</v>
       </c>
       <c r="AJ8">
-        <v>0.501626877551233</v>
+        <v>0.4843257796098484</v>
       </c>
       <c r="AK8">
-        <v>0.588951449017641</v>
+        <v>0.5880409529808602</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1446,10 +1446,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>6909.744463373083</v>
+        <v>8532.063492063491</v>
       </c>
       <c r="AP8">
-        <v>3892.316991193757</v>
+        <v>4828.409219913246</v>
       </c>
     </row>
     <row r="9">
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.00371</v>
+        <v>-0.007209999999999999</v>
       </c>
       <c r="E9">
-        <v>0.0188</v>
+        <v>-0.04219999999999999</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1487,85 +1487,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>166.2</v>
+        <v>130.4</v>
       </c>
       <c r="L9">
-        <v>0.231896190874843</v>
+        <v>0.1878962536023055</v>
       </c>
       <c r="M9">
-        <v>80.59999999999999</v>
+        <v>58.42400000000001</v>
       </c>
       <c r="N9">
-        <v>0.07793463546702764</v>
+        <v>0.06342850939094562</v>
       </c>
       <c r="O9">
-        <v>0.4849578820697954</v>
+        <v>0.448036809815951</v>
       </c>
       <c r="P9">
-        <v>68</v>
+        <v>58.42400000000001</v>
       </c>
       <c r="Q9">
-        <v>0.06575130535679752</v>
+        <v>0.06342850939094562</v>
       </c>
       <c r="R9">
-        <v>0.4091456077015644</v>
+        <v>0.448036809815951</v>
       </c>
       <c r="S9">
-        <v>12.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>0.1563275434243176</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>58.4</v>
+        <v>50</v>
       </c>
       <c r="V9">
-        <v>0.05646876812995551</v>
+        <v>0.05428292259255238</v>
       </c>
       <c r="W9">
-        <v>0.08180744240992321</v>
+        <v>0.06687522437048053</v>
       </c>
       <c r="X9">
-        <v>0.2935618483325673</v>
+        <v>0.2355410852590686</v>
       </c>
       <c r="Y9">
-        <v>-0.2117544059226441</v>
+        <v>-0.1686658608885881</v>
       </c>
       <c r="Z9">
-        <v>0.05183299462649435</v>
+        <v>0.04978372057990144</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06386219224548187</v>
+        <v>0.05294432321601062</v>
       </c>
       <c r="AC9">
-        <v>-0.06386219224548187</v>
+        <v>-0.05294432321601062</v>
       </c>
       <c r="AD9">
-        <v>12020.7</v>
+        <v>12363.1</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>12020.7</v>
+        <v>12363.1</v>
       </c>
       <c r="AG9">
-        <v>11962.3</v>
+        <v>12313.1</v>
       </c>
       <c r="AH9">
-        <v>0.9207807030310458</v>
+        <v>0.9306619894310534</v>
       </c>
       <c r="AI9">
-        <v>0.8549512450124822</v>
+        <v>0.8572686613736435</v>
       </c>
       <c r="AJ9">
-        <v>0.9204247297349286</v>
+        <v>0.9304000241797766</v>
       </c>
       <c r="AK9">
-        <v>0.8543462579543913</v>
+        <v>0.8567720836377553</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/research/traditional_assets/database/data/canada/canada_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0539</v>
+        <v>0.0416</v>
       </c>
       <c r="E2">
-        <v>-0.0106</v>
+        <v>0.0484</v>
       </c>
       <c r="F2">
-        <v>0.0442</v>
+        <v>0.08825</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>1.699213933192129e-05</v>
+        <v>3.633407618908792E-06</v>
       </c>
       <c r="J2">
-        <v>1.3398023285596e-05</v>
+        <v>2.972816923122066E-06</v>
       </c>
       <c r="K2">
-        <v>33069.1</v>
+        <v>36651.85</v>
       </c>
       <c r="L2">
-        <v>0.2377462451678396</v>
+        <v>0.2537659668895402</v>
       </c>
       <c r="M2">
-        <v>30490.04</v>
+        <v>36164.633</v>
       </c>
       <c r="N2">
-        <v>0.06601070285610118</v>
+        <v>0.07343579658291131</v>
       </c>
       <c r="O2">
-        <v>0.9220099730564182</v>
+        <v>0.9867068920122724</v>
       </c>
       <c r="P2">
-        <v>18740.34</v>
+        <v>20164.533</v>
       </c>
       <c r="Q2">
-        <v>0.0405726924320961</v>
+        <v>0.04094604094495864</v>
       </c>
       <c r="R2">
-        <v>0.5667024503237161</v>
+        <v>0.5501641254124963</v>
       </c>
       <c r="S2">
-        <v>11749.7</v>
+        <v>16000.1</v>
       </c>
       <c r="T2">
-        <v>0.3853619083477753</v>
+        <v>0.4424239560235548</v>
       </c>
       <c r="U2">
-        <v>140597.1</v>
+        <v>113565.6</v>
       </c>
       <c r="V2">
-        <v>0.3043916436491899</v>
+        <v>0.230605970767525</v>
       </c>
       <c r="W2">
-        <v>0.100071285209157</v>
+        <v>0.1010204933352205</v>
       </c>
       <c r="X2">
-        <v>0.09370581980287165</v>
+        <v>0.1022502755672436</v>
       </c>
       <c r="Y2">
-        <v>0.006365465406285339</v>
+        <v>-0.001229782232023136</v>
       </c>
       <c r="Z2">
-        <v>0.1055184962194647</v>
+        <v>0.100857989783612</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05061526714808874</v>
+        <v>0.05458272590835781</v>
       </c>
       <c r="AC2">
-        <v>-0.05061526714808874</v>
+        <v>-0.05458272590835781</v>
       </c>
       <c r="AD2">
-        <v>1278458.2</v>
+        <v>1376575.3</v>
       </c>
       <c r="AE2">
-        <v>13.38246836275903</v>
+        <v>90.92610380404025</v>
       </c>
       <c r="AF2">
-        <v>1278471.582468363</v>
+        <v>1376666.226103804</v>
       </c>
       <c r="AG2">
-        <v>1137874.482468363</v>
+        <v>1263100.626103804</v>
       </c>
       <c r="AH2">
-        <v>0.7345988491778361</v>
+        <v>0.736526933128459</v>
       </c>
       <c r="AI2">
-        <v>0.7923568596509138</v>
+        <v>0.7938742825535604</v>
       </c>
       <c r="AJ2">
-        <v>0.7112738494068164</v>
+        <v>0.719483161346631</v>
       </c>
       <c r="AK2">
-        <v>0.7725361854053631</v>
+        <v>0.7794292759800543</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>253662.3412698413</v>
+        <v>73574.30785676109</v>
       </c>
       <c r="AP2">
-        <v>225768.7465215005</v>
+        <v>67509.38675060417</v>
       </c>
     </row>
     <row r="3">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0621</v>
+        <v>0.0696</v>
       </c>
       <c r="E3">
-        <v>-0.008670000000000001</v>
+        <v>-0.05400000000000001</v>
       </c>
       <c r="F3">
-        <v>0.018</v>
+        <v>0.0429</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -740,85 +740,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>7763.1</v>
+        <v>6345.2</v>
       </c>
       <c r="L3">
-        <v>0.2191424675863587</v>
+        <v>0.1660664558949771</v>
       </c>
       <c r="M3">
-        <v>13758.032</v>
+        <v>16039.307</v>
       </c>
       <c r="N3">
-        <v>0.1185058546476272</v>
+        <v>0.1723298411037322</v>
       </c>
       <c r="O3">
-        <v>1.772234287848926</v>
+        <v>2.527785885393683</v>
       </c>
       <c r="P3">
-        <v>4942.331999999999</v>
+        <v>5127.207</v>
       </c>
       <c r="Q3">
-        <v>0.04257115244479128</v>
+        <v>0.05508783936961513</v>
       </c>
       <c r="R3">
-        <v>0.6366441241256714</v>
+        <v>0.8080449788816744</v>
       </c>
       <c r="S3">
-        <v>8815.700000000001</v>
+        <v>10912.1</v>
       </c>
       <c r="T3">
-        <v>0.6407675167494887</v>
+        <v>0.6803348798049691</v>
       </c>
       <c r="U3">
-        <v>4839.2</v>
+        <v>4619.3</v>
       </c>
       <c r="V3">
-        <v>0.04168281712172189</v>
+        <v>0.04963077488388185</v>
       </c>
       <c r="W3">
-        <v>0.100071285209157</v>
+        <v>0.08241118834616544</v>
       </c>
       <c r="X3">
-        <v>0.09327393304184414</v>
+        <v>0.1104516432656275</v>
       </c>
       <c r="Y3">
-        <v>0.006797352167312851</v>
+        <v>-0.0280404549194621</v>
       </c>
       <c r="Z3">
-        <v>0.1023461827149593</v>
+        <v>0.1012073212724817</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05002928962713915</v>
+        <v>0.05415091083320916</v>
       </c>
       <c r="AC3">
-        <v>-0.05002928962713915</v>
+        <v>-0.05415091083320916</v>
       </c>
       <c r="AD3">
-        <v>317231.2</v>
+        <v>353382.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>317231.2</v>
+        <v>353382.1</v>
       </c>
       <c r="AG3">
-        <v>312392</v>
+        <v>348762.8</v>
       </c>
       <c r="AH3">
-        <v>0.732082699670226</v>
+        <v>0.7915283363131009</v>
       </c>
       <c r="AI3">
-        <v>0.7971658665637388</v>
+        <v>0.8104668355721684</v>
       </c>
       <c r="AJ3">
-        <v>0.7290569299756026</v>
+        <v>0.7893488105657279</v>
       </c>
       <c r="AK3">
-        <v>0.7946689676365065</v>
+        <v>0.8084373890250337</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada (TSX:RY)</t>
+          <t>Canadian Imperial Bank of Commerce (TSX:CM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0539</v>
+        <v>0.0638</v>
       </c>
       <c r="E4">
-        <v>0.0368</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F4">
-        <v>0.0516</v>
+        <v>0.0852</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -865,85 +865,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>10698.5</v>
+        <v>5105.8</v>
       </c>
       <c r="L4">
-        <v>0.2769035257090501</v>
+        <v>0.3014156345561236</v>
       </c>
       <c r="M4">
-        <v>6759.4</v>
+        <v>2734.992</v>
       </c>
       <c r="N4">
-        <v>0.04736309204740934</v>
+        <v>0.04592380152799933</v>
       </c>
       <c r="O4">
-        <v>0.6318081974108519</v>
+        <v>0.5356637549453562</v>
       </c>
       <c r="P4">
-        <v>3825.4</v>
+        <v>2431.392</v>
       </c>
       <c r="Q4">
-        <v>0.02680456435751098</v>
+        <v>0.04082599277978339</v>
       </c>
       <c r="R4">
-        <v>0.3575641445062392</v>
+        <v>0.476201966391163</v>
       </c>
       <c r="S4">
-        <v>2934</v>
+        <v>303.5999999999999</v>
       </c>
       <c r="T4">
-        <v>0.434062194869367</v>
+        <v>0.1110058091577599</v>
       </c>
       <c r="U4">
-        <v>43192.4</v>
+        <v>5812</v>
       </c>
       <c r="V4">
-        <v>0.302648995021529</v>
+        <v>0.09759046259759886</v>
       </c>
       <c r="W4">
-        <v>0.1448150303883482</v>
+        <v>0.1409639818224988</v>
       </c>
       <c r="X4">
-        <v>0.09116715327413334</v>
+        <v>0.1024151697364169</v>
       </c>
       <c r="Y4">
-        <v>0.05364787711421486</v>
+        <v>0.03854881208608193</v>
       </c>
       <c r="Z4">
-        <v>0.1080539427906612</v>
+        <v>0.09229052604739021</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05014077194846574</v>
+        <v>0.05450457842896154</v>
       </c>
       <c r="AC4">
-        <v>-0.05014077194846574</v>
+        <v>-0.05450457842896154</v>
       </c>
       <c r="AD4">
-        <v>367375.2</v>
+        <v>187939.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>367375.2</v>
+        <v>187939.7</v>
       </c>
       <c r="AG4">
-        <v>324182.8</v>
+        <v>182127.7</v>
       </c>
       <c r="AH4">
-        <v>0.7202168559765076</v>
+        <v>0.7593685844585762</v>
       </c>
       <c r="AI4">
-        <v>0.812484173292413</v>
+        <v>0.8161206891310824</v>
       </c>
       <c r="AJ4">
-        <v>0.6943342786518577</v>
+        <v>0.7535818658100063</v>
       </c>
       <c r="AK4">
-        <v>0.7926801566372146</v>
+        <v>0.8113597140314035</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Canadian Imperial Bank of Commerce (TSX:CM)</t>
+          <t>The Bank of Nova Scotia (TSX:BNS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,13 +969,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0467</v>
+        <v>0.0112</v>
       </c>
       <c r="E5">
-        <v>-0.0106</v>
-      </c>
-      <c r="F5">
-        <v>0.0368</v>
+        <v>-0.0155</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -990,28 +987,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>3596.4</v>
+        <v>5567.3</v>
       </c>
       <c r="L5">
-        <v>0.234361865041869</v>
+        <v>0.2631360037811651</v>
       </c>
       <c r="M5">
-        <v>2309.128</v>
+        <v>3730.2</v>
       </c>
       <c r="N5">
-        <v>0.05133654363475485</v>
+        <v>0.05654971256700706</v>
       </c>
       <c r="O5">
-        <v>0.6420665109553999</v>
+        <v>0.6700195786108166</v>
       </c>
       <c r="P5">
-        <v>2309.128</v>
+        <v>3730.2</v>
       </c>
       <c r="Q5">
-        <v>0.05133654363475485</v>
+        <v>0.05654971256700706</v>
       </c>
       <c r="R5">
-        <v>0.6420665109553999</v>
+        <v>0.6700195786108166</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1020,55 +1017,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>14634.1</v>
+        <v>2930.7</v>
       </c>
       <c r="V5">
-        <v>0.3253453741868645</v>
+        <v>0.04442931816528004</v>
       </c>
       <c r="W5">
-        <v>0.1031249462353258</v>
+        <v>0.1010204933352205</v>
       </c>
       <c r="X5">
-        <v>0.1023142611331278</v>
+        <v>0.1022502755672436</v>
       </c>
       <c r="Y5">
-        <v>0.0008106851021980749</v>
+        <v>-0.001229782232023136</v>
       </c>
       <c r="Z5">
-        <v>0.096138545257257</v>
+        <v>0.09137568178156989</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05049035222616338</v>
+        <v>0.05451298109622928</v>
       </c>
       <c r="AC5">
-        <v>-0.05049035222616338</v>
+        <v>-0.05451298109622928</v>
       </c>
       <c r="AD5">
-        <v>153461.8</v>
+        <v>207294.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>153461.8</v>
+        <v>207294.6</v>
       </c>
       <c r="AG5">
-        <v>138827.7</v>
+        <v>204363.9</v>
       </c>
       <c r="AH5">
-        <v>0.7733332661432559</v>
+        <v>0.7586045119297602</v>
       </c>
       <c r="AI5">
-        <v>0.8002162946863883</v>
+        <v>0.7745595581943661</v>
       </c>
       <c r="AJ5">
-        <v>0.7552869055138545</v>
+        <v>0.7559874685149954</v>
       </c>
       <c r="AK5">
-        <v>0.7837116471427047</v>
+        <v>0.7720635153304725</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1085,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia (TSX:BNS)</t>
+          <t>Bank of Montreal (TSX:BMO)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1094,10 +1091,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0226</v>
+        <v>0.0336</v>
       </c>
       <c r="E6">
-        <v>-0.0282</v>
+        <v>0.0491</v>
+      </c>
+      <c r="F6">
+        <v>0.113</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1112,28 +1112,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>5335.2</v>
+        <v>5251.5</v>
       </c>
       <c r="L6">
-        <v>0.2533140881984275</v>
+        <v>0.2520482066492923</v>
       </c>
       <c r="M6">
-        <v>3602.2</v>
+        <v>3202.944</v>
       </c>
       <c r="N6">
-        <v>0.06075120205483495</v>
+        <v>0.04526431970198231</v>
       </c>
       <c r="O6">
-        <v>0.6751761883340831</v>
+        <v>0.6099103113396173</v>
       </c>
       <c r="P6">
-        <v>3602.2</v>
+        <v>3202.944</v>
       </c>
       <c r="Q6">
-        <v>0.06075120205483495</v>
+        <v>0.04526431970198231</v>
       </c>
       <c r="R6">
-        <v>0.6751761883340831</v>
+        <v>0.6099103113396173</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1142,55 +1142,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>3178.8</v>
+        <v>46658.1</v>
       </c>
       <c r="V6">
-        <v>0.05361054941200082</v>
+        <v>0.6593768592541926</v>
       </c>
       <c r="W6">
-        <v>0.09976849341197326</v>
+        <v>0.1001951817021447</v>
       </c>
       <c r="X6">
-        <v>0.09865756493975505</v>
+        <v>0.1009208606181575</v>
       </c>
       <c r="Y6">
-        <v>0.001110928472218206</v>
+        <v>-0.0007256789160127869</v>
       </c>
       <c r="Z6">
-        <v>0.09625819000819</v>
+        <v>0.112174363883336</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05061526714808874</v>
+        <v>0.05458272590835781</v>
       </c>
       <c r="AC6">
-        <v>-0.05061526714808874</v>
+        <v>-0.05458272590835781</v>
       </c>
       <c r="AD6">
-        <v>186006.7</v>
+        <v>214867.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>186006.7</v>
+        <v>214867.6</v>
       </c>
       <c r="AG6">
-        <v>182827.9</v>
+        <v>168209.5</v>
       </c>
       <c r="AH6">
-        <v>0.7582794199779047</v>
+        <v>0.7522624668056584</v>
       </c>
       <c r="AI6">
-        <v>0.7665723047402547</v>
+        <v>0.7803359109970593</v>
       </c>
       <c r="AJ6">
-        <v>0.7551058928094987</v>
+        <v>0.7038926159892606</v>
       </c>
       <c r="AK6">
-        <v>0.7634736927821405</v>
+        <v>0.7355202090473496</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bank of Montreal (TSX:BMO)</t>
+          <t>Royal Bank of Canada (TSX:RY)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1216,13 +1216,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0546</v>
+        <v>0.0416</v>
       </c>
       <c r="E7">
-        <v>-0.0435</v>
+        <v>0.04769999999999999</v>
       </c>
       <c r="F7">
-        <v>0.0635</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1237,85 +1237,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>3142.8</v>
+        <v>11646.9</v>
       </c>
       <c r="L7">
-        <v>0.150407029331955</v>
+        <v>0.2999327868725809</v>
       </c>
       <c r="M7">
-        <v>3030.5</v>
+        <v>9316.200000000001</v>
       </c>
       <c r="N7">
-        <v>0.04210244070509259</v>
+        <v>0.05465707470070086</v>
       </c>
       <c r="O7">
-        <v>0.9642675321369479</v>
+        <v>0.7998866651211911</v>
       </c>
       <c r="P7">
-        <v>3030.5</v>
+        <v>4531.8</v>
       </c>
       <c r="Q7">
-        <v>0.04210244070509259</v>
+        <v>0.02658754976585262</v>
       </c>
       <c r="R7">
-        <v>0.9642675321369479</v>
+        <v>0.3890992452927389</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>4784.400000000001</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.5135570296902171</v>
       </c>
       <c r="U7">
-        <v>56022.8</v>
+        <v>39270.2</v>
       </c>
       <c r="V7">
-        <v>0.7783192922399805</v>
+        <v>0.2303937501246713</v>
       </c>
       <c r="W7">
-        <v>0.06266937061431059</v>
+        <v>0.1501488996893089</v>
       </c>
       <c r="X7">
-        <v>0.09370581980287165</v>
+        <v>0.08931306296622152</v>
       </c>
       <c r="Y7">
-        <v>-0.03103644918856106</v>
+        <v>0.06083583672308734</v>
       </c>
       <c r="Z7">
-        <v>0.1132728136140095</v>
+        <v>0.09740306649456115</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05081348245462826</v>
+        <v>0.05504465419277597</v>
       </c>
       <c r="AC7">
-        <v>-0.05081348245462826</v>
+        <v>-0.05504465419277597</v>
       </c>
       <c r="AD7">
-        <v>199018.6</v>
+        <v>359740.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>199018.6</v>
+        <v>359740.9</v>
       </c>
       <c r="AG7">
-        <v>142995.8</v>
+        <v>320470.7</v>
       </c>
       <c r="AH7">
-        <v>0.7343919397131637</v>
+        <v>0.6785143263035772</v>
       </c>
       <c r="AI7">
-        <v>0.7820426774638722</v>
+        <v>0.7976231890613218</v>
       </c>
       <c r="AJ7">
-        <v>0.6651740900104662</v>
+        <v>0.652797641321204</v>
       </c>
       <c r="AK7">
-        <v>0.7205168928383556</v>
+        <v>0.7783215327705753</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>National Bank of Canada (TSX:NA)</t>
+          <t>Laurentian Bank of Canada (TSX:LB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1341,10 +1341,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.07400000000000001</v>
-      </c>
-      <c r="E8">
-        <v>0.0924</v>
+        <v>0.00695</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1353,34 +1350,34 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.0003358875490219984</v>
+        <v>-0.002416135849360832</v>
       </c>
       <c r="J8">
-        <v>0.0002820262147160826</v>
+        <v>-0.002416135849360832</v>
       </c>
       <c r="K8">
-        <v>2402.7</v>
+        <v>-3.95</v>
       </c>
       <c r="L8">
-        <v>0.3414575220987408</v>
+        <v>-0.005753823743627094</v>
       </c>
       <c r="M8">
-        <v>972.3560000000001</v>
+        <v>59.40000000000001</v>
       </c>
       <c r="N8">
-        <v>0.03752777852823009</v>
+        <v>0.0670655978322231</v>
       </c>
       <c r="O8">
-        <v>0.4046930536479794</v>
+        <v>-15.0379746835443</v>
       </c>
       <c r="P8">
-        <v>972.3560000000001</v>
+        <v>59.40000000000001</v>
       </c>
       <c r="Q8">
-        <v>0.03752777852823009</v>
+        <v>0.0670655978322231</v>
       </c>
       <c r="R8">
-        <v>0.4046930536479794</v>
+        <v>-15.0379746835443</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1389,55 +1386,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>18679.8</v>
+        <v>52.8</v>
       </c>
       <c r="V8">
-        <v>0.7209410929244354</v>
+        <v>0.05961386473975386</v>
       </c>
       <c r="W8">
-        <v>0.1630618463647531</v>
+        <v>-0.00200507614213198</v>
       </c>
       <c r="X8">
-        <v>0.07900217716469986</v>
+        <v>0.251291609638572</v>
       </c>
       <c r="Y8">
-        <v>0.08405966920005321</v>
+        <v>-0.253296685780704</v>
       </c>
       <c r="Z8">
-        <v>0.1867795832738809</v>
+        <v>0.04643221556230017</v>
       </c>
       <c r="AA8">
-        <v>5.267673885697998e-05</v>
+        <v>-0.0001121865405853234</v>
       </c>
       <c r="AB8">
-        <v>0.05241320603286936</v>
+        <v>0.05550762580797872</v>
       </c>
       <c r="AC8">
-        <v>-0.05236052929401239</v>
+        <v>-0.05561981234856404</v>
       </c>
       <c r="AD8">
-        <v>43001.6</v>
+        <v>13233.4</v>
       </c>
       <c r="AE8">
-        <v>13.38246836275903</v>
+        <v>80.29338630293105</v>
       </c>
       <c r="AF8">
-        <v>43014.98246836276</v>
+        <v>13313.69338630293</v>
       </c>
       <c r="AG8">
-        <v>24335.18246836276</v>
+        <v>13260.89338630293</v>
       </c>
       <c r="AH8">
-        <v>0.6240813374701362</v>
+        <v>0.9376240959100148</v>
       </c>
       <c r="AI8">
-        <v>0.7161610338399358</v>
+        <v>0.8677093964916756</v>
       </c>
       <c r="AJ8">
-        <v>0.4843257796098484</v>
+        <v>0.9373912873711662</v>
       </c>
       <c r="AK8">
-        <v>0.5880409529808602</v>
+        <v>0.8672525863465257</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1446,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>8532.063492063491</v>
+        <v>918.9861111111111</v>
       </c>
       <c r="AP8">
-        <v>4828.409219913246</v>
+        <v>920.8953740488146</v>
       </c>
     </row>
     <row r="9">
@@ -1460,7 +1457,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Laurentian Bank of Canada (TSX:LB)</t>
+          <t>National Bank of Canada (TSX:NA)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1469,10 +1466,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.007209999999999999</v>
+        <v>0.0886</v>
       </c>
       <c r="E9">
-        <v>-0.04219999999999999</v>
+        <v>0.111</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1481,34 +1478,34 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>0.0002809207461921081</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>0.0002244104499422677</v>
       </c>
       <c r="K9">
-        <v>130.4</v>
+        <v>2739.1</v>
       </c>
       <c r="L9">
-        <v>0.1878962536023055</v>
+        <v>0.3524091347700225</v>
       </c>
       <c r="M9">
-        <v>58.42400000000001</v>
+        <v>1081.59</v>
       </c>
       <c r="N9">
-        <v>0.06342850939094562</v>
+        <v>0.03403399025163862</v>
       </c>
       <c r="O9">
-        <v>0.448036809815951</v>
+        <v>0.3948705779270563</v>
       </c>
       <c r="P9">
-        <v>58.42400000000001</v>
+        <v>1081.59</v>
       </c>
       <c r="Q9">
-        <v>0.06342850939094562</v>
+        <v>0.03403399025163862</v>
       </c>
       <c r="R9">
-        <v>0.448036809815951</v>
+        <v>0.3948705779270563</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1517,61 +1514,67 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>50</v>
+        <v>14222.5</v>
       </c>
       <c r="V9">
-        <v>0.05428292259255238</v>
+        <v>0.4475341176914823</v>
       </c>
       <c r="W9">
-        <v>0.06687522437048053</v>
+        <v>0.1734584671112209</v>
       </c>
       <c r="X9">
-        <v>0.2355410852590686</v>
+        <v>0.07868424043574057</v>
       </c>
       <c r="Y9">
-        <v>-0.1686658608885881</v>
+        <v>0.0947742266754803</v>
       </c>
       <c r="Z9">
-        <v>0.04978372057990144</v>
+        <v>0.1932667687011836</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>4.337108252312081E-05</v>
       </c>
       <c r="AB9">
-        <v>0.05294432321601062</v>
+        <v>0.05671856039122702</v>
       </c>
       <c r="AC9">
-        <v>-0.05294432321601062</v>
+        <v>-0.0566751893087039</v>
       </c>
       <c r="AD9">
-        <v>12363.1</v>
+        <v>40117</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>10.6327175011092</v>
       </c>
       <c r="AF9">
-        <v>12363.1</v>
+        <v>40127.63271750111</v>
       </c>
       <c r="AG9">
-        <v>12313.1</v>
+        <v>25905.13271750111</v>
       </c>
       <c r="AH9">
-        <v>0.9306619894310534</v>
+        <v>0.5580464634274312</v>
       </c>
       <c r="AI9">
-        <v>0.8572686613736435</v>
+        <v>0.686379696128859</v>
       </c>
       <c r="AJ9">
-        <v>0.9304000241797766</v>
+        <v>0.4490804861022281</v>
       </c>
       <c r="AK9">
-        <v>0.8567720836377553</v>
+        <v>0.5855559775853808</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
         <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>9307.888631090487</v>
+      </c>
+      <c r="AP9">
+        <v>6010.471628190513</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/canada/canada_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_bank_money_center.xlsx
@@ -648,10 +648,10 @@
         <v>0.1010204933352205</v>
       </c>
       <c r="X2">
-        <v>0.1022502755672436</v>
+        <v>0.1022139830590778</v>
       </c>
       <c r="Y2">
-        <v>-0.001229782232023136</v>
+        <v>-0.001193489723857383</v>
       </c>
       <c r="Z2">
         <v>0.100857989783612</v>
@@ -660,10 +660,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05458272590835781</v>
+        <v>0.05457394663209425</v>
       </c>
       <c r="AC2">
-        <v>-0.05458272590835781</v>
+        <v>-0.05457394663209425</v>
       </c>
       <c r="AD2">
         <v>1376575.3</v>
@@ -779,10 +779,10 @@
         <v>0.08241118834616544</v>
       </c>
       <c r="X3">
-        <v>0.1104516432656275</v>
+        <v>0.1104100780072197</v>
       </c>
       <c r="Y3">
-        <v>-0.0280404549194621</v>
+        <v>-0.02799888966105422</v>
       </c>
       <c r="Z3">
         <v>0.1012073212724817</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05415091083320916</v>
+        <v>0.05414224565463729</v>
       </c>
       <c r="AC3">
-        <v>-0.05415091083320916</v>
+        <v>-0.05414224565463729</v>
       </c>
       <c r="AD3">
         <v>353382.1</v>
@@ -904,10 +904,10 @@
         <v>0.1409639818224988</v>
       </c>
       <c r="X4">
-        <v>0.1024151697364169</v>
+        <v>0.1023787712159612</v>
       </c>
       <c r="Y4">
-        <v>0.03854881208608193</v>
+        <v>0.03858521060653765</v>
       </c>
       <c r="Z4">
         <v>0.09229052604739021</v>
@@ -916,10 +916,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05450457842896154</v>
+        <v>0.05449581980146066</v>
       </c>
       <c r="AC4">
-        <v>-0.05450457842896154</v>
+        <v>-0.05449581980146066</v>
       </c>
       <c r="AD4">
         <v>187939.7</v>
@@ -1026,10 +1026,10 @@
         <v>0.1010204933352205</v>
       </c>
       <c r="X5">
-        <v>0.1022502755672436</v>
+        <v>0.1022139830590778</v>
       </c>
       <c r="Y5">
-        <v>-0.001229782232023136</v>
+        <v>-0.001193489723857383</v>
       </c>
       <c r="Z5">
         <v>0.09137568178156989</v>
@@ -1038,10 +1038,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05451298109622928</v>
+        <v>0.05450422024850731</v>
       </c>
       <c r="AC5">
-        <v>-0.05451298109622928</v>
+        <v>-0.05450422024850731</v>
       </c>
       <c r="AD5">
         <v>207294.6</v>
@@ -1151,10 +1151,10 @@
         <v>0.1001951817021447</v>
       </c>
       <c r="X6">
-        <v>0.1009208606181575</v>
+        <v>0.100885422805605</v>
       </c>
       <c r="Y6">
-        <v>-0.0007256789160127869</v>
+        <v>-0.0006902411034602901</v>
       </c>
       <c r="Z6">
         <v>0.112174363883336</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05458272590835781</v>
+        <v>0.05457394663209425</v>
       </c>
       <c r="AC6">
-        <v>-0.05458272590835781</v>
+        <v>-0.05457394663209425</v>
       </c>
       <c r="AD6">
         <v>214867.6</v>
@@ -1276,10 +1276,10 @@
         <v>0.1501488996893089</v>
       </c>
       <c r="X7">
-        <v>0.08931306296622152</v>
+        <v>0.08928508793550377</v>
       </c>
       <c r="Y7">
-        <v>0.06083583672308734</v>
+        <v>0.06086381175380509</v>
       </c>
       <c r="Z7">
         <v>0.09740306649456115</v>
@@ -1288,10 +1288,10 @@
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05504465419277597</v>
+        <v>0.055035660621179</v>
       </c>
       <c r="AC7">
-        <v>-0.05504465419277597</v>
+        <v>-0.055035660621179</v>
       </c>
       <c r="AD7">
         <v>359740.9</v>
@@ -1395,10 +1395,10 @@
         <v>-0.00200507614213198</v>
       </c>
       <c r="X8">
-        <v>0.251291609638572</v>
+        <v>0.2511594968039425</v>
       </c>
       <c r="Y8">
-        <v>-0.253296685780704</v>
+        <v>-0.2531645729460745</v>
       </c>
       <c r="Z8">
         <v>0.04643221556230017</v>
@@ -1407,10 +1407,10 @@
         <v>-0.0001121865405853234</v>
       </c>
       <c r="AB8">
-        <v>0.05550762580797872</v>
+        <v>0.05549938515047682</v>
       </c>
       <c r="AC8">
-        <v>-0.05561981234856404</v>
+        <v>-0.05561157169106214</v>
       </c>
       <c r="AD8">
         <v>13233.4</v>
@@ -1523,10 +1523,10 @@
         <v>0.1734584671112209</v>
       </c>
       <c r="X9">
-        <v>0.07868424043574057</v>
+        <v>0.07866309879289568</v>
       </c>
       <c r="Y9">
-        <v>0.0947742266754803</v>
+        <v>0.09479536831832519</v>
       </c>
       <c r="Z9">
         <v>0.1932667687011836</v>
@@ -1535,10 +1535,10 @@
         <v>4.337108252312081E-05</v>
       </c>
       <c r="AB9">
-        <v>0.05671856039122702</v>
+        <v>0.05670921676740277</v>
       </c>
       <c r="AC9">
-        <v>-0.0566751893087039</v>
+        <v>-0.05666584568487965</v>
       </c>
       <c r="AD9">
         <v>40117</v>
